--- a/source/guides/cdc/opioid-cds/ValueSet-xylazine-urine-drug-screening-tests.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-xylazine-urine-drug-screening-tests.xlsx
@@ -8,13 +8,15 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId6" sheetId="4"/>
+    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -28,10 +30,16 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/xylazine-urine-drug-screening-tests</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.4.642.40.65.48.69</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2022.1.0</t>
+    <t>2022.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-09T18:08:12-06:00</t>
+    <t>2026-06-02T10:00:16-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,36 +117,57 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>parent</t>
+    <t>concept</t>
+  </si>
+  <si>
+    <t>is-a</t>
+  </si>
+  <si>
+    <t>LP437281-1</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
   <si>
     <t>=</t>
   </si>
   <si>
-    <t>LP436919-7</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
     <t>LP7681-2</t>
   </si>
   <si>
+    <t>CLASSTYPE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>System URI</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
+    <t>LP435271-4</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>http://loinc.org|2.82</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -151,10 +180,28 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2.81</t>
+    <t>103638-3</t>
+  </si>
+  <si>
+    <t>4-hydroxy Xylazine [Mass/volume] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>103639-1</t>
+  </si>
+  <si>
+    <t>4-hydroxy Xylazine [Presence] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>103640-9</t>
+  </si>
+  <si>
+    <t>4-hydroxy Xylazine/Creatinine [Mass Ratio] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>101808-4</t>
+  </si>
+  <si>
+    <t>Xylazine [Mass/volume] in Urine by Confirmatory method</t>
   </si>
   <si>
     <t>101809-2</t>
@@ -163,16 +210,16 @@
     <t>Xylazine [Presence] in Urine by Confirmatory method</t>
   </si>
   <si>
-    <t>101808-4</t>
-  </si>
-  <si>
-    <t>Xylazine [Mass/volume] in Urine by Confirmatory method</t>
-  </si>
-  <si>
     <t>101810-0</t>
   </si>
   <si>
     <t>Xylazine/Creatinine [Mass Ratio] in Urine by Confirmatory method</t>
+  </si>
+  <si>
+    <t>107608-2</t>
+  </si>
+  <si>
+    <t>Xylazine [Presence] in Urine</t>
   </si>
 </sst>
 </file>
@@ -306,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -433,6 +480,14 @@
         <v>29</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -440,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -452,7 +507,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -460,40 +515,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -503,30 +569,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>42</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -534,68 +659,195 @@
         <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
